--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/28.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/28.xlsx
@@ -426,13 +426,13 @@
         <v>-21.73852529296388</v>
       </c>
       <c r="E2">
-        <v>-20.87111893935579</v>
+        <v>-25.80651701262327</v>
       </c>
       <c r="F2">
-        <v>-0.9817091250814383</v>
+        <v>-1.945067279841151</v>
       </c>
       <c r="G2">
-        <v>-16.33327058202219</v>
+        <v>-17.68132985701583</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.87889119260756</v>
       </c>
       <c r="E3">
-        <v>-20.47816284985714</v>
+        <v>-25.63881449253802</v>
       </c>
       <c r="F3">
-        <v>-1.377777259749369</v>
+        <v>-1.71018618787956</v>
       </c>
       <c r="G3">
-        <v>-15.81104595220639</v>
+        <v>-17.18854267783713</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.78214676757152</v>
       </c>
       <c r="E4">
-        <v>-21.90635254739388</v>
+        <v>-25.60933499855438</v>
       </c>
       <c r="F4">
-        <v>-0.4000709532057654</v>
+        <v>-1.740251782764168</v>
       </c>
       <c r="G4">
-        <v>-16.04925159407186</v>
+        <v>-16.84464756806192</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.57002595463469</v>
       </c>
       <c r="E5">
-        <v>-21.90325009853423</v>
+        <v>-25.94398000105245</v>
       </c>
       <c r="F5">
-        <v>-0.9419425195426452</v>
+        <v>-1.806652057037771</v>
       </c>
       <c r="G5">
-        <v>-15.6127990616802</v>
+        <v>-16.57532446141497</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.24148853359949</v>
       </c>
       <c r="E6">
-        <v>-21.09228159561424</v>
+        <v>-26.75407632959422</v>
       </c>
       <c r="F6">
-        <v>-0.6999399530191864</v>
+        <v>-1.950766447572412</v>
       </c>
       <c r="G6">
-        <v>-15.83139540092182</v>
+        <v>-16.79176693636892</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.86274995242386</v>
       </c>
       <c r="E7">
-        <v>-23.14735285730927</v>
+        <v>-27.16685984995761</v>
       </c>
       <c r="F7">
-        <v>-1.480941307726616</v>
+        <v>-1.686213235242542</v>
       </c>
       <c r="G7">
-        <v>-15.18559770274716</v>
+        <v>-16.33642436148826</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.46082401082738</v>
       </c>
       <c r="E8">
-        <v>-22.91952014366315</v>
+        <v>-27.3821083332895</v>
       </c>
       <c r="F8">
-        <v>-0.827278246912332</v>
+        <v>-1.918246400073309</v>
       </c>
       <c r="G8">
-        <v>-13.93072634518871</v>
+        <v>-16.09181586851308</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.08174977747001</v>
       </c>
       <c r="E9">
-        <v>-23.35231798940088</v>
+        <v>-27.99308725128503</v>
       </c>
       <c r="F9">
-        <v>-0.5754421309502403</v>
+        <v>-1.487703270835669</v>
       </c>
       <c r="G9">
-        <v>-14.75905686219566</v>
+        <v>-15.38789646887875</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.75850797886919</v>
       </c>
       <c r="E10">
-        <v>-23.70729296133398</v>
+        <v>-28.22988259497012</v>
       </c>
       <c r="F10">
-        <v>-0.2804646406503504</v>
+        <v>-1.387544539795778</v>
       </c>
       <c r="G10">
-        <v>-14.47553130497305</v>
+        <v>-15.23497993668806</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.51014549258838</v>
       </c>
       <c r="E11">
-        <v>-23.74733822492798</v>
+        <v>-29.80977456596321</v>
       </c>
       <c r="F11">
-        <v>-0.2047195537057664</v>
+        <v>-1.479817213161017</v>
       </c>
       <c r="G11">
-        <v>-13.31759036722117</v>
+        <v>-14.91011454423747</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.36800827330649</v>
       </c>
       <c r="E12">
-        <v>-23.68668472674018</v>
+        <v>-29.67770867565065</v>
       </c>
       <c r="F12">
-        <v>-0.5499574078031135</v>
+        <v>-1.276069481666243</v>
       </c>
       <c r="G12">
-        <v>-14.10832485674378</v>
+        <v>-14.1303242960408</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.3251138778709</v>
       </c>
       <c r="E13">
-        <v>-25.08198099058428</v>
+        <v>-30.31386020748597</v>
       </c>
       <c r="F13">
-        <v>-0.0134843118302781</v>
+        <v>-1.50852594223984</v>
       </c>
       <c r="G13">
-        <v>-12.50880518959559</v>
+        <v>-14.36159318952769</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.405415200211951</v>
       </c>
       <c r="E14">
-        <v>-25.7910836793402</v>
+        <v>-29.97619789696042</v>
       </c>
       <c r="F14">
-        <v>0.2986834588125072</v>
+        <v>-1.287296345076384</v>
       </c>
       <c r="G14">
-        <v>-11.86748622376698</v>
+        <v>-13.34448756337111</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.590397669774545</v>
       </c>
       <c r="E15">
-        <v>-26.25803753501333</v>
+        <v>-31.32657925693216</v>
       </c>
       <c r="F15">
-        <v>-0.6958552733559821</v>
+        <v>-1.116451366820806</v>
       </c>
       <c r="G15">
-        <v>-11.06063299713882</v>
+        <v>-13.25654202107487</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.882595526984082</v>
       </c>
       <c r="E16">
-        <v>-26.23067202559403</v>
+        <v>-31.22867560637197</v>
       </c>
       <c r="F16">
-        <v>0.2396258331973192</v>
+        <v>-0.8771608751741127</v>
       </c>
       <c r="G16">
-        <v>-12.72792889924462</v>
+        <v>-12.93293761826179</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.259911467736296</v>
       </c>
       <c r="E17">
-        <v>-26.53101150254901</v>
+        <v>-31.7624982409805</v>
       </c>
       <c r="F17">
-        <v>-0.1421363964242637</v>
+        <v>-0.8733884900217637</v>
       </c>
       <c r="G17">
-        <v>-10.19510720194229</v>
+        <v>-13.03196054985812</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.708763800234514</v>
       </c>
       <c r="E18">
-        <v>-29.34038277524242</v>
+        <v>-33.11032537598746</v>
       </c>
       <c r="F18">
-        <v>0.6577658173128424</v>
+        <v>-0.7059058550541485</v>
       </c>
       <c r="G18">
-        <v>-10.51178791009974</v>
+        <v>-12.46465880393216</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.212728828172438</v>
       </c>
       <c r="E19">
-        <v>-27.88119973819414</v>
+        <v>-33.74968734017687</v>
       </c>
       <c r="F19">
-        <v>0.5141716415071593</v>
+        <v>-0.6504450007019159</v>
       </c>
       <c r="G19">
-        <v>-9.848071366423962</v>
+        <v>-11.85971925860841</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.754045593872796</v>
       </c>
       <c r="E20">
-        <v>-28.91279513311168</v>
+        <v>-33.96749004847353</v>
       </c>
       <c r="F20">
-        <v>0.9430737749198538</v>
+        <v>-0.5561188045451363</v>
       </c>
       <c r="G20">
-        <v>-10.10206157008731</v>
+        <v>-11.68560478571018</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.329999797983847</v>
       </c>
       <c r="E21">
-        <v>-28.77322231332949</v>
+        <v>-34.26466477839899</v>
       </c>
       <c r="F21">
-        <v>0.4660998243878985</v>
+        <v>-0.570394888364983</v>
       </c>
       <c r="G21">
-        <v>-9.50362930565691</v>
+        <v>-11.92904758122543</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.927452741469644</v>
       </c>
       <c r="E22">
-        <v>-30.01165386204048</v>
+        <v>-35.13294344439029</v>
       </c>
       <c r="F22">
-        <v>1.252874899892841</v>
+        <v>-0.2744954251457771</v>
       </c>
       <c r="G22">
-        <v>-9.362600798961855</v>
+        <v>-11.31770779553657</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.557961725039029</v>
       </c>
       <c r="E23">
-        <v>-30.96718526814944</v>
+        <v>-35.55795401889397</v>
       </c>
       <c r="F23">
-        <v>1.144531070545888</v>
+        <v>-0.1355699280222721</v>
       </c>
       <c r="G23">
-        <v>-9.735903335811372</v>
+        <v>-11.7380402854504</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.222103002666508</v>
       </c>
       <c r="E24">
-        <v>-30.71824801115621</v>
+        <v>-35.84454636636377</v>
       </c>
       <c r="F24">
-        <v>1.571385479738862</v>
+        <v>-0.05310015450176166</v>
       </c>
       <c r="G24">
-        <v>-9.281347900424933</v>
+        <v>-11.3417879982727</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.935882637267475</v>
       </c>
       <c r="E25">
-        <v>-34.31277973159713</v>
+        <v>-35.45601552353172</v>
       </c>
       <c r="F25">
-        <v>0.7345968939224966</v>
+        <v>-0.05274975509037747</v>
       </c>
       <c r="G25">
-        <v>-10.03247739450036</v>
+        <v>-11.23141224382191</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.707743278617931</v>
       </c>
       <c r="E26">
-        <v>-31.40254772188026</v>
+        <v>-35.98527377889425</v>
       </c>
       <c r="F26">
-        <v>0.4823242283391296</v>
+        <v>-0.3393151744148384</v>
       </c>
       <c r="G26">
-        <v>-8.559591893744118</v>
+        <v>-10.72322950378941</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.54784936130267</v>
       </c>
       <c r="E27">
-        <v>-31.54430720742497</v>
+        <v>-35.70620082052806</v>
       </c>
       <c r="F27">
-        <v>0.7876604530110274</v>
+        <v>-0.02511127669597197</v>
       </c>
       <c r="G27">
-        <v>-9.510213603515696</v>
+        <v>-11.00051146532237</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.462979664348641</v>
       </c>
       <c r="E28">
-        <v>-31.00268899515974</v>
+        <v>-35.84844623179778</v>
       </c>
       <c r="F28">
-        <v>1.409007244707297</v>
+        <v>-0.2053814192606032</v>
       </c>
       <c r="G28">
-        <v>-8.651785117490101</v>
+        <v>-10.9039674357153</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.450722297840904</v>
       </c>
       <c r="E29">
-        <v>-31.94427807085126</v>
+        <v>-35.59571293965365</v>
       </c>
       <c r="F29">
-        <v>1.323756641815589</v>
+        <v>-0.105735447643045</v>
       </c>
       <c r="G29">
-        <v>-9.870079943327047</v>
+        <v>-11.31182839871738</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.508819433927197</v>
       </c>
       <c r="E30">
-        <v>-31.15670460732402</v>
+        <v>-35.52588084443799</v>
       </c>
       <c r="F30">
-        <v>1.262333198898006</v>
+        <v>-0.1302211597023956</v>
       </c>
       <c r="G30">
-        <v>-9.772874089966127</v>
+        <v>-11.03650319025546</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.620720979901132</v>
       </c>
       <c r="E31">
-        <v>-31.12416627319965</v>
+        <v>-35.23542185722477</v>
       </c>
       <c r="F31">
-        <v>0.7444213313196988</v>
+        <v>-0.06721636341286803</v>
       </c>
       <c r="G31">
-        <v>-10.50250410233374</v>
+        <v>-11.14772352058148</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.773196584815121</v>
       </c>
       <c r="E32">
-        <v>-31.4550713088997</v>
+        <v>-35.23542393383044</v>
       </c>
       <c r="F32">
-        <v>1.554695533307258</v>
+        <v>0.08699251229228792</v>
       </c>
       <c r="G32">
-        <v>-10.4069482395544</v>
+        <v>-11.49294749935357</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.943359132252327</v>
       </c>
       <c r="E33">
-        <v>-31.89165273015436</v>
+        <v>-35.69186601164042</v>
       </c>
       <c r="F33">
-        <v>0.9208669015856047</v>
+        <v>-0.06461694650288319</v>
       </c>
       <c r="G33">
-        <v>-10.53279135033524</v>
+        <v>-11.51584634016222</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.113025930832379</v>
       </c>
       <c r="E34">
-        <v>-30.95437468781801</v>
+        <v>-34.58123292860573</v>
       </c>
       <c r="F34">
-        <v>1.166370148753294</v>
+        <v>-0.1163534610121291</v>
       </c>
       <c r="G34">
-        <v>-10.25429147645053</v>
+        <v>-10.97880312404726</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.264059089301993</v>
       </c>
       <c r="E35">
-        <v>-30.56759650016504</v>
+        <v>-34.01332488865434</v>
       </c>
       <c r="F35">
-        <v>1.17649445515031</v>
+        <v>0.06202966060892483</v>
       </c>
       <c r="G35">
-        <v>-9.276315690225562</v>
+        <v>-11.24139312039373</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.382917392703326</v>
       </c>
       <c r="E36">
-        <v>-29.93345512261094</v>
+        <v>-33.78753140176871</v>
       </c>
       <c r="F36">
-        <v>1.180184003562379</v>
+        <v>-0.2854812336417042</v>
       </c>
       <c r="G36">
-        <v>-10.19477172126233</v>
+        <v>-11.44951254159122</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.463096331405609</v>
       </c>
       <c r="E37">
-        <v>-29.69170707442099</v>
+        <v>-33.77991441219898</v>
       </c>
       <c r="F37">
-        <v>1.540757423387753</v>
+        <v>-0.009968720572797003</v>
       </c>
       <c r="G37">
-        <v>-10.9692438827269</v>
+        <v>-11.04851000462999</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.500465276046785</v>
       </c>
       <c r="E38">
-        <v>-28.58368013149263</v>
+        <v>-33.22699738852455</v>
       </c>
       <c r="F38">
-        <v>1.119875543168964</v>
+        <v>-0.2137644973769342</v>
       </c>
       <c r="G38">
-        <v>-9.573444532140165</v>
+        <v>-11.67730783939962</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.500984726382726</v>
       </c>
       <c r="E39">
-        <v>-28.81339632647456</v>
+        <v>-32.67353006434958</v>
       </c>
       <c r="F39">
-        <v>0.7503872333546608</v>
+        <v>-0.05780445298226005</v>
       </c>
       <c r="G39">
-        <v>-10.63628518204386</v>
+        <v>-11.48035065670145</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.470666472677</v>
       </c>
       <c r="E40">
-        <v>-26.25403799250752</v>
+        <v>-32.59989570416604</v>
       </c>
       <c r="F40">
-        <v>1.690645534719907</v>
+        <v>-0.1055366394663732</v>
       </c>
       <c r="G40">
-        <v>-11.2520684550268</v>
+        <v>-11.70905449362756</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.423822028022314</v>
       </c>
       <c r="E41">
-        <v>-29.35475703963765</v>
+        <v>-31.67056483169976</v>
       </c>
       <c r="F41">
-        <v>1.311470296497267</v>
+        <v>0.06404922033695003</v>
       </c>
       <c r="G41">
-        <v>-10.3188147236476</v>
+        <v>-11.5303960197685</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.371847284081965</v>
       </c>
       <c r="E42">
-        <v>-27.97450163060642</v>
+        <v>-31.23162853962393</v>
       </c>
       <c r="F42">
-        <v>1.676074552104664</v>
+        <v>0.06209510163374599</v>
       </c>
       <c r="G42">
-        <v>-10.24804657538859</v>
+        <v>-11.38390975150572</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.327807766575194</v>
       </c>
       <c r="E43">
-        <v>-28.05436996098853</v>
+        <v>-31.06365190759124</v>
       </c>
       <c r="F43">
-        <v>1.286342599700746</v>
+        <v>0.08462172478547575</v>
       </c>
       <c r="G43">
-        <v>-10.80374747772394</v>
+        <v>-11.62524437076364</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.298650699076485</v>
       </c>
       <c r="E44">
-        <v>-28.27388171574536</v>
+        <v>-31.15696625963749</v>
       </c>
       <c r="F44">
-        <v>1.212387614713612</v>
+        <v>-0.08513229360061575</v>
       </c>
       <c r="G44">
-        <v>-10.37934483699256</v>
+        <v>-11.53266867293506</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.286796915108153</v>
       </c>
       <c r="E45">
-        <v>-26.39105243411361</v>
+        <v>-30.15016138311785</v>
       </c>
       <c r="F45">
-        <v>1.275847184707277</v>
+        <v>0.06210669877738518</v>
       </c>
       <c r="G45">
-        <v>-10.3518341158637</v>
+        <v>-11.70470760388336</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.295630130883255</v>
       </c>
       <c r="E46">
-        <v>-25.69815142273584</v>
+        <v>-29.83135465200702</v>
       </c>
       <c r="F46">
-        <v>1.64277915271654</v>
+        <v>-0.2070050193700902</v>
       </c>
       <c r="G46">
-        <v>-11.3839763254928</v>
+        <v>-11.84833510681886</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.323624511550085</v>
       </c>
       <c r="E47">
-        <v>-25.33807215408453</v>
+        <v>-29.87670148985716</v>
       </c>
       <c r="F47">
-        <v>1.491926821727528</v>
+        <v>0.2739798861262203</v>
       </c>
       <c r="G47">
-        <v>-10.73122751984429</v>
+        <v>-12.05520920284639</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.374367884114175</v>
       </c>
       <c r="E48">
-        <v>-24.14564365061301</v>
+        <v>-29.28645955600651</v>
       </c>
       <c r="F48">
-        <v>1.357843960440789</v>
+        <v>0.4976854734566436</v>
       </c>
       <c r="G48">
-        <v>-12.11166394388462</v>
+        <v>-11.88062349054946</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.44248854261532</v>
       </c>
       <c r="E49">
-        <v>-24.70418412242125</v>
+        <v>-29.16878038972315</v>
       </c>
       <c r="F49">
-        <v>1.387809322869658</v>
+        <v>0.4016843184114033</v>
       </c>
       <c r="G49">
-        <v>-10.76145602609249</v>
+        <v>-12.00856694535385</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.529860392975508</v>
       </c>
       <c r="E50">
-        <v>-24.96739389013226</v>
+        <v>-28.44191233952527</v>
       </c>
       <c r="F50">
-        <v>1.344151047272513</v>
+        <v>0.217518363951406</v>
       </c>
       <c r="G50">
-        <v>-10.74515975835476</v>
+        <v>-12.28039636680827</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.631289555005005</v>
       </c>
       <c r="E51">
-        <v>-24.02580273783508</v>
+        <v>-28.01496636854422</v>
       </c>
       <c r="F51">
-        <v>1.863671604347056</v>
+        <v>0.01794808926894914</v>
       </c>
       <c r="G51">
-        <v>-10.11848315356541</v>
+        <v>-12.63649670754694</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.748000075976271</v>
       </c>
       <c r="E52">
-        <v>-23.93759268250705</v>
+        <v>-28.35706430876468</v>
       </c>
       <c r="F52">
-        <v>0.7878012754695033</v>
+        <v>0.0684486796132182</v>
       </c>
       <c r="G52">
-        <v>-10.23536357816496</v>
+        <v>-12.22379411870064</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.881063395184156</v>
       </c>
       <c r="E53">
-        <v>-22.90137061017365</v>
+        <v>-26.96169951693373</v>
       </c>
       <c r="F53">
-        <v>1.707188031753813</v>
+        <v>0.3324543410898375</v>
       </c>
       <c r="G53">
-        <v>-10.84969266641064</v>
+        <v>-12.54809820106414</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.032463240488052</v>
       </c>
       <c r="E54">
-        <v>-21.42419378506056</v>
+        <v>-27.21811047770599</v>
       </c>
       <c r="F54">
-        <v>1.447519701998252</v>
+        <v>-0.09967511172416386</v>
       </c>
       <c r="G54">
-        <v>-11.51900534111747</v>
+        <v>-12.04886639886228</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.209887168569227</v>
       </c>
       <c r="E55">
-        <v>-24.01650785089011</v>
+        <v>-26.4168106507502</v>
       </c>
       <c r="F55">
-        <v>1.601369066250593</v>
+        <v>-0.02498453648334364</v>
       </c>
       <c r="G55">
-        <v>-10.9956841985734</v>
+        <v>-12.48564396895553</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.41333614845878</v>
       </c>
       <c r="E56">
-        <v>-24.11325275549067</v>
+        <v>-26.68007441020843</v>
       </c>
       <c r="F56">
-        <v>1.345600690227412</v>
+        <v>-0.1868375865815334</v>
       </c>
       <c r="G56">
-        <v>-11.88531891469657</v>
+        <v>-12.68041726380324</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.65244938897606</v>
       </c>
       <c r="E57">
-        <v>-21.7665471477775</v>
+        <v>-25.62998476526143</v>
       </c>
       <c r="F57">
-        <v>1.329361375662931</v>
+        <v>0.1226984608225578</v>
       </c>
       <c r="G57">
-        <v>-11.65256581290964</v>
+        <v>-12.97899637433821</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.922473453758992</v>
       </c>
       <c r="E58">
-        <v>-20.8763229131458</v>
+        <v>-26.08659297152441</v>
       </c>
       <c r="F58">
-        <v>1.01182164241299</v>
+        <v>0.1187777979051078</v>
       </c>
       <c r="G58">
-        <v>-11.35106397380493</v>
+        <v>-13.08915935310482</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.229187449606588</v>
       </c>
       <c r="E59">
-        <v>-21.4771264633955</v>
+        <v>-26.00754905359027</v>
       </c>
       <c r="F59">
-        <v>0.5563935280278501</v>
+        <v>0.2452984931716903</v>
       </c>
       <c r="G59">
-        <v>-11.78262919232202</v>
+        <v>-13.32883876029198</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.565950583255308</v>
       </c>
       <c r="E60">
-        <v>-20.12523125789586</v>
+        <v>-24.95843956651593</v>
       </c>
       <c r="F60">
-        <v>1.065236429280308</v>
+        <v>-0.07762397146164103</v>
       </c>
       <c r="G60">
-        <v>-11.28146413375044</v>
+        <v>-13.03404261866953</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.931043370525718</v>
       </c>
       <c r="E61">
-        <v>-20.49860495599795</v>
+        <v>-25.31902968016019</v>
       </c>
       <c r="F61">
-        <v>0.6688791943888006</v>
+        <v>-0.07125382613411282</v>
       </c>
       <c r="G61">
-        <v>-10.21452592021099</v>
+        <v>-13.03934243018949</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.318902220808151</v>
       </c>
       <c r="E62">
-        <v>-20.27735092909036</v>
+        <v>-24.10507092918076</v>
       </c>
       <c r="F62">
-        <v>1.104176324151107</v>
+        <v>-0.2307493426039352</v>
       </c>
       <c r="G62">
-        <v>-11.61760011060086</v>
+        <v>-13.64295180114407</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.720849190137174</v>
       </c>
       <c r="E63">
-        <v>-20.64902181054926</v>
+        <v>-24.48901455010454</v>
       </c>
       <c r="F63">
-        <v>0.850611405419373</v>
+        <v>-0.1028427886724692</v>
       </c>
       <c r="G63">
-        <v>-12.12698509851757</v>
+        <v>-13.83789740513479</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.13426760378102</v>
       </c>
       <c r="E64">
-        <v>-19.62161285264715</v>
+        <v>-23.89632222157223</v>
       </c>
       <c r="F64">
-        <v>0.8302584183325892</v>
+        <v>-0.2898401029152352</v>
       </c>
       <c r="G64">
-        <v>-12.46251668799515</v>
+        <v>-13.7077491765232</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.545295702779705</v>
       </c>
       <c r="E65">
-        <v>-20.65010995191637</v>
+        <v>-24.70620258312512</v>
       </c>
       <c r="F65">
-        <v>1.469300794487462</v>
+        <v>-0.3534603761850428</v>
       </c>
       <c r="G65">
-        <v>-11.04734561254235</v>
+        <v>-13.70923730094014</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.954561160056842</v>
       </c>
       <c r="E66">
-        <v>-20.43998653135932</v>
+        <v>-24.26344948984177</v>
       </c>
       <c r="F66">
-        <v>0.8602701693360152</v>
+        <v>-0.3174620139615847</v>
       </c>
       <c r="G66">
-        <v>-12.58279238593544</v>
+        <v>-13.8925663968727</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.34547062725522</v>
       </c>
       <c r="E67">
-        <v>-19.57581123815694</v>
+        <v>-25.00147098905248</v>
       </c>
       <c r="F67">
-        <v>1.258287452502733</v>
+        <v>-0.2664991946065535</v>
       </c>
       <c r="G67">
-        <v>-11.83823413599585</v>
+        <v>-13.88185973330455</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.720153206745281</v>
       </c>
       <c r="E68">
-        <v>-20.12538492671488</v>
+        <v>-24.09073404368745</v>
       </c>
       <c r="F68">
-        <v>0.8408449537403668</v>
+        <v>-0.4093619219955646</v>
       </c>
       <c r="G68">
-        <v>-12.35649304477774</v>
+        <v>-13.43627351096088</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.067239147235535</v>
       </c>
       <c r="E69">
-        <v>-18.86725262008457</v>
+        <v>-24.19147849079382</v>
       </c>
       <c r="F69">
-        <v>1.148296828759015</v>
+        <v>-0.7329396252445103</v>
       </c>
       <c r="G69">
-        <v>-11.73411242021307</v>
+        <v>-13.53438137657803</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.388107694282017</v>
       </c>
       <c r="E70">
-        <v>-21.09777214098566</v>
+        <v>-23.82772363012003</v>
       </c>
       <c r="F70">
-        <v>0.7276932799875655</v>
+        <v>-0.3524936714259758</v>
       </c>
       <c r="G70">
-        <v>-12.1848196180722</v>
+        <v>-13.41867839778907</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.680403630235983</v>
       </c>
       <c r="E71">
-        <v>-19.41740775822798</v>
+        <v>-24.46379209772885</v>
       </c>
       <c r="F71">
-        <v>0.6352764706942386</v>
+        <v>-0.6481951548359125</v>
       </c>
       <c r="G71">
-        <v>-12.4103566218093</v>
+        <v>-13.40555679547414</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.943973729986144</v>
       </c>
       <c r="E72">
-        <v>-19.02075531065023</v>
+        <v>-24.40752439070007</v>
       </c>
       <c r="F72">
-        <v>0.3917058046772804</v>
+        <v>-0.5734996093906755</v>
       </c>
       <c r="G72">
-        <v>-11.90953226540686</v>
+        <v>-13.61975664082432</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.184807448998351</v>
       </c>
       <c r="E73">
-        <v>-20.07321228605238</v>
+        <v>-24.00930202924154</v>
       </c>
       <c r="F73">
-        <v>0.3253444636716093</v>
+        <v>-0.6152758342486602</v>
       </c>
       <c r="G73">
-        <v>-11.83211977216346</v>
+        <v>-13.3883232704282</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.398255751851163</v>
       </c>
       <c r="E74">
-        <v>-18.62043557747266</v>
+        <v>-24.42159131745727</v>
       </c>
       <c r="F74">
-        <v>0.4883124962939672</v>
+        <v>-0.875866136923537</v>
       </c>
       <c r="G74">
-        <v>-12.32632458565514</v>
+        <v>-13.64614604715129</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.593850555399298</v>
       </c>
       <c r="E75">
-        <v>-19.26685800091427</v>
+        <v>-24.27697234591541</v>
       </c>
       <c r="F75">
-        <v>0.8951775716899864</v>
+        <v>-0.6863149659779402</v>
       </c>
       <c r="G75">
-        <v>-10.90242840177884</v>
+        <v>-12.91359200084164</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.76059788829439</v>
       </c>
       <c r="E76">
-        <v>-21.74406996808753</v>
+        <v>-25.56812268257811</v>
       </c>
       <c r="F76">
-        <v>0.5932285413281358</v>
+        <v>-0.5651132178047333</v>
       </c>
       <c r="G76">
-        <v>-11.37954719729397</v>
+        <v>-12.90964063890299</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.907554530330454</v>
       </c>
       <c r="E77">
-        <v>-20.26700527968021</v>
+        <v>-25.09523804113313</v>
       </c>
       <c r="F77">
-        <v>0.7044956792395682</v>
+        <v>-0.8998821646655003</v>
       </c>
       <c r="G77">
-        <v>-10.66964136031222</v>
+        <v>-13.04012695893912</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.02200701217713</v>
       </c>
       <c r="E78">
-        <v>-22.10527475700787</v>
+        <v>-25.73524790628921</v>
       </c>
       <c r="F78">
-        <v>0.510086961843955</v>
+        <v>-0.72621079683157</v>
       </c>
       <c r="G78">
-        <v>-11.48604207991007</v>
+        <v>-13.09113568676029</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.10673496203296</v>
       </c>
       <c r="E79">
-        <v>-22.72133720566498</v>
+        <v>-26.00286423121586</v>
       </c>
       <c r="F79">
-        <v>0.06365657418802306</v>
+        <v>-0.878526853021329</v>
       </c>
       <c r="G79">
-        <v>-11.65867103913596</v>
+        <v>-12.68616090190369</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.15149869493762</v>
       </c>
       <c r="E80">
-        <v>-22.33891781329742</v>
+        <v>-25.74855064216264</v>
       </c>
       <c r="F80">
-        <v>0.4521675130402136</v>
+        <v>-1.030458546736189</v>
       </c>
       <c r="G80">
-        <v>-11.59695956386352</v>
+        <v>-12.81940677897263</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.15159934600445</v>
       </c>
       <c r="E81">
-        <v>-21.66404173906941</v>
+        <v>-26.96186564538672</v>
       </c>
       <c r="F81">
-        <v>0.3208522272462276</v>
+        <v>-1.055484354342165</v>
       </c>
       <c r="G81">
-        <v>-11.25276160771574</v>
+        <v>-12.55447233398334</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.1008905418548</v>
       </c>
       <c r="E82">
-        <v>-22.11004264360877</v>
+        <v>-27.10476103422877</v>
       </c>
       <c r="F82">
-        <v>0.2931632184402513</v>
+        <v>-1.248727558802039</v>
       </c>
       <c r="G82">
-        <v>-10.61599055896484</v>
+        <v>-11.79732246288081</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.989423387521201</v>
       </c>
       <c r="E83">
-        <v>-23.1707769691813</v>
+        <v>-28.28298140175806</v>
       </c>
       <c r="F83">
-        <v>0.3229645641233663</v>
+        <v>-1.120300790141615</v>
       </c>
       <c r="G83">
-        <v>-10.91830956112658</v>
+        <v>-11.79215710470729</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.8176630589962</v>
       </c>
       <c r="E84">
-        <v>-23.11809348352585</v>
+        <v>-28.32034784404754</v>
       </c>
       <c r="F84">
-        <v>0.421988431821422</v>
+        <v>-0.8696624934439715</v>
       </c>
       <c r="G84">
-        <v>-11.27909096691712</v>
+        <v>-12.23520176719151</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.574249600810852</v>
       </c>
       <c r="E85">
-        <v>-24.31458382767306</v>
+        <v>-28.83388204133428</v>
       </c>
       <c r="F85">
-        <v>0.02458745400238717</v>
+        <v>-1.002506117096123</v>
       </c>
       <c r="G85">
-        <v>-10.3268049074687</v>
+        <v>-12.1364634067556</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.267801424289638</v>
       </c>
       <c r="E86">
-        <v>-27.13628806139555</v>
+        <v>-30.10281892722613</v>
       </c>
       <c r="F86">
-        <v>0.5313064212340671</v>
+        <v>-1.167730622523707</v>
       </c>
       <c r="G86">
-        <v>-9.916856654166024</v>
+        <v>-11.61443588815643</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.890711294944452</v>
       </c>
       <c r="E87">
-        <v>-26.19843895250204</v>
+        <v>-30.99342941051103</v>
       </c>
       <c r="F87">
-        <v>-0.234840649206362</v>
+        <v>-1.090982382654332</v>
       </c>
       <c r="G87">
-        <v>-10.52332348507557</v>
+        <v>-11.58052231591787</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.456825634556145</v>
       </c>
       <c r="E88">
-        <v>-27.48197645280633</v>
+        <v>-31.1041021092894</v>
       </c>
       <c r="F88">
-        <v>0.2165450322531166</v>
+        <v>-1.0037718624876</v>
       </c>
       <c r="G88">
-        <v>-9.887483166771409</v>
+        <v>-11.50144677836994</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.967000055433171</v>
       </c>
       <c r="E89">
-        <v>-28.32795652719463</v>
+        <v>-32.7923658999869</v>
       </c>
       <c r="F89">
-        <v>0.6884551728517586</v>
+        <v>-1.129345733812783</v>
       </c>
       <c r="G89">
-        <v>-11.25486456248388</v>
+        <v>-11.22135957177383</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.436111501049223</v>
       </c>
       <c r="E90">
-        <v>-30.60625459117654</v>
+        <v>-33.51144044913374</v>
       </c>
       <c r="F90">
-        <v>-0.02713083642399716</v>
+        <v>-1.379506062519011</v>
       </c>
       <c r="G90">
-        <v>-9.533779489567381</v>
+        <v>-11.53851021395768</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.873116399111541</v>
       </c>
       <c r="E91">
-        <v>-30.88591107573387</v>
+        <v>-34.48999725882756</v>
       </c>
       <c r="F91">
-        <v>-0.1047198692072129</v>
+        <v>-1.32121964695583</v>
       </c>
       <c r="G91">
-        <v>-10.31150855490937</v>
+        <v>-11.1052062395429</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.290865589203084</v>
       </c>
       <c r="E92">
-        <v>-31.3614558490324</v>
+        <v>-36.13683484316556</v>
       </c>
       <c r="F92">
-        <v>-0.4578363256725861</v>
+        <v>-1.32445690676597</v>
       </c>
       <c r="G92">
-        <v>-10.71017708620614</v>
+        <v>-11.02663588107335</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.701789826413851</v>
       </c>
       <c r="E93">
-        <v>-33.81932008124895</v>
+        <v>-37.17654561301181</v>
       </c>
       <c r="F93">
-        <v>-0.3262534772074958</v>
+        <v>-1.58747432593105</v>
       </c>
       <c r="G93">
-        <v>-10.26500466688016</v>
+        <v>-11.12589247431059</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.110685654586865</v>
       </c>
       <c r="E94">
-        <v>-33.81012487137578</v>
+        <v>-38.86413450686903</v>
       </c>
       <c r="F94">
-        <v>0.03164017406982216</v>
+        <v>-1.494924977853275</v>
       </c>
       <c r="G94">
-        <v>-10.3400544362686</v>
+        <v>-10.93997090899905</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.530099761090278</v>
       </c>
       <c r="E95">
-        <v>-36.86730372758207</v>
+        <v>-40.9377124782275</v>
       </c>
       <c r="F95">
-        <v>-0.09608413903302801</v>
+        <v>-1.724298254953652</v>
       </c>
       <c r="G95">
-        <v>-10.46504122282356</v>
+        <v>-11.32976029794144</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.95179757314357</v>
       </c>
       <c r="E96">
-        <v>-40.64079732400985</v>
+        <v>-42.00592258418473</v>
       </c>
       <c r="F96">
-        <v>-0.7376066471918827</v>
+        <v>-1.791030704555778</v>
       </c>
       <c r="G96">
-        <v>-10.04815622114229</v>
+        <v>-11.36649086359381</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.386551075003884</v>
       </c>
       <c r="E97">
-        <v>-40.56322156627904</v>
+        <v>-43.29298200769247</v>
       </c>
       <c r="F97">
-        <v>-0.3574249425748413</v>
+        <v>-1.799994468221471</v>
       </c>
       <c r="G97">
-        <v>-9.951056102937313</v>
+        <v>-11.12393311049496</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.816555851332667</v>
       </c>
       <c r="E98">
-        <v>-43.48125330686393</v>
+        <v>-44.57478138905731</v>
       </c>
       <c r="F98">
-        <v>-1.484487548578001</v>
+        <v>-1.930696762137385</v>
       </c>
       <c r="G98">
-        <v>-10.87189835453036</v>
+        <v>-11.29761028367418</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.254902617780494</v>
       </c>
       <c r="E99">
-        <v>-43.67537025097509</v>
+        <v>-46.57649219165095</v>
       </c>
       <c r="F99">
-        <v>-1.182848327624797</v>
+        <v>-2.16513799100809</v>
       </c>
       <c r="G99">
-        <v>-10.27135269235345</v>
+        <v>-11.33620883708149</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.676682746893039</v>
       </c>
       <c r="E100">
-        <v>-46.22734209860093</v>
+        <v>-48.08975834657114</v>
       </c>
       <c r="F100">
-        <v>-1.021876660443186</v>
+        <v>-2.064802817711403</v>
       </c>
       <c r="G100">
-        <v>-11.25039627311619</v>
+        <v>-11.84785603518639</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.115260352000412</v>
       </c>
       <c r="E101">
-        <v>-50.22274385271996</v>
+        <v>-49.47698388250826</v>
       </c>
       <c r="F101">
-        <v>-1.136835831868896</v>
+        <v>-2.433279690926887</v>
       </c>
       <c r="G101">
-        <v>-10.98662491484224</v>
+        <v>-11.5572475278881</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.5254683642446328</v>
       </c>
       <c r="E102">
-        <v>-49.76443490641947</v>
+        <v>-51.58549139941137</v>
       </c>
       <c r="F102">
-        <v>-1.436008174696563</v>
+        <v>-2.740224605095022</v>
       </c>
       <c r="G102">
-        <v>-10.71867114373333</v>
+        <v>-11.56524554394297</v>
       </c>
     </row>
   </sheetData>
